--- a/docs/generated/Документы.xlsx
+++ b/docs/generated/Документы.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2166,28 +2166,137 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0024</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00088</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>INV-2026-0012</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00088</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0012</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00088</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5">
-        <f>SUM(F2:F46)</f>
+      <c r="B50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5">
+        <f>SUM(F2:F49)</f>
         <v/>
       </c>
-      <c r="G47" s="5">
-        <f>SUM(G2:G46)</f>
+      <c r="G50" s="5">
+        <f>SUM(G2:G49)</f>
         <v/>
       </c>
-      <c r="H47" s="5">
-        <f>SUM(H2:H46)</f>
+      <c r="H50" s="5">
+        <f>SUM(H2:H49)</f>
         <v/>
       </c>
-      <c r="I47" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>

--- a/docs/generated/Документы.xlsx
+++ b/docs/generated/Документы.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2275,28 +2275,211 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0025</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0026</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0027</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00097</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>INV-2026-0013</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00097</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0013</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00097</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr"/>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5">
-        <f>SUM(F2:F49)</f>
+      <c r="B55" s="5" t="inlineStr"/>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5">
+        <f>SUM(F2:F54)</f>
         <v/>
       </c>
-      <c r="G50" s="5">
-        <f>SUM(G2:G49)</f>
+      <c r="G55" s="5">
+        <f>SUM(G2:G54)</f>
         <v/>
       </c>
-      <c r="H50" s="5">
-        <f>SUM(H2:H49)</f>
+      <c r="H55" s="5">
+        <f>SUM(H2:H54)</f>
         <v/>
       </c>
-      <c r="I50" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>

--- a/docs/generated/Документы.xlsx
+++ b/docs/generated/Документы.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,33 +525,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0001</t>
+          <t>СЧ-2026-0011</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00001</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -567,14 +563,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0002</t>
+          <t>KP-2026-0028</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -599,37 +595,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0003</t>
+          <t>СЧ-2026-0001</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00018</t>
-        </is>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="4" t="n">
-        <v>62480</v>
+        <v>23820</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>23820</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>issued</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -641,28 +633,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0001</t>
+          <t>СЧ-2026-0003</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00018</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="4" t="n">
-        <v>62480</v>
+        <v>70000</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>62480</v>
+        <v>70000</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -673,31 +661,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0001</t>
+          <t>СЧ-2026-0004</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00018</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="4" t="n">
-        <v>62480</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>62480</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -708,70 +694,62 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0004</t>
+          <t>СЧ-2026-0005</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00021</t>
-        </is>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="4" t="n">
-        <v>62480</v>
+        <v>10000</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>issued</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>credit_note</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0002</t>
+          <t>КН-2026-0001</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00021</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="4" t="n">
-        <v>62480</v>
+        <v>5000</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>62480</v>
+        <v>5000</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -782,31 +760,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0002</t>
+          <t>СЧ-2026-0007</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00021</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="4" t="n">
-        <v>62480</v>
+        <v>12000</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>62480</v>
+        <v>12000</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -817,33 +793,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0005</t>
+          <t>СЧ-2026-0008</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00024</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="4" t="n">
-        <v>62480</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>62480</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -859,63 +831,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0003</t>
+          <t>СЧ-2026-0009</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00024</t>
-        </is>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="4" t="n">
-        <v>62480</v>
+        <v>10000</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>issued</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>credit_note</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0003</t>
+          <t>КН-2026-0002</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00024</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="4" t="n">
-        <v>62480</v>
+        <v>5000</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>62480</v>
+        <v>5000</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -926,33 +892,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0006</t>
+          <t>СЧ-2026-0012</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00027</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="4" t="n">
-        <v>62480</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>62480</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -968,63 +930,57 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0004</t>
+          <t>СЧ-2026-0013</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00027</t>
-        </is>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="4" t="n">
-        <v>62480</v>
+        <v>10000</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>issued</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>credit_note</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0004</t>
+          <t>КН-2026-0003</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00027</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="4" t="n">
-        <v>62480</v>
+        <v>5000</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>62480</v>
+        <v>5000</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1035,33 +991,29 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0007</t>
+          <t>СЧ-2026-0015</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00001</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1077,14 +1029,14 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0008</t>
+          <t>KP-2026-0029</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1114,28 +1066,28 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0009</t>
+          <t>KP-2026-0030</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00106</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1146,23 +1098,23 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0010</t>
+          <t>INV-2026-0029</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00040</t>
+          <t>DIM-2026-00106</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -1183,23 +1135,21 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>Акт выполненных работ</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0005</t>
+          <t>ACT-2026-0014</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>46291</v>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D20" s="3" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00040</t>
+          <t>DIM-2026-00106</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -1913,12 +1863,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0021</t>
+          <t>INV-2026-0003</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -1929,7 +1879,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00077</t>
+          <t>DIM-2026-00024</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
@@ -2458,28 +2408,855 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0001</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0002</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0003</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00018</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>INV-2026-0001</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00018</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0001</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00018</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0004</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00021</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>INV-2026-0002</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00021</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0002</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00021</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0005</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00024</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0003</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00024</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0021</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00077</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0006</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00027</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>INV-2026-0004</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00027</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0004</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00027</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0007</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0008</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0009</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0010</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00040</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>INV-2026-0005</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00040</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0014</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0006</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0010</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0002</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="4" t="n">
+        <v>64800</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>64800</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5">
-        <f>SUM(F2:F54)</f>
+      <c r="B78" s="5" t="inlineStr"/>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5">
+        <f>SUM(F2:F77)</f>
         <v/>
       </c>
-      <c r="G55" s="5">
-        <f>SUM(G2:G54)</f>
+      <c r="G78" s="5">
+        <f>SUM(G2:G77)</f>
         <v/>
       </c>
-      <c r="H55" s="5">
-        <f>SUM(H2:H54)</f>
+      <c r="H78" s="5">
+        <f>SUM(H2:H77)</f>
         <v/>
       </c>
-      <c r="I55" s="5" t="inlineStr"/>
+      <c r="I78" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>

--- a/docs/generated/Документы.xlsx
+++ b/docs/generated/Документы.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,29 +525,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>Коммерческое предложение</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0011</t>
+          <t>KP-2026-0030</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+        <v>46292</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00106</t>
+        </is>
+      </c>
       <c r="F2" s="4" t="n">
-        <v>12000</v>
+        <v>62480</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>12000</v>
+        <v>62480</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -897,7 +901,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0012</t>
+          <t>СЧ-2026-0011</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -908,13 +912,13 @@
       </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="4" t="n">
-        <v>9028.799999999999</v>
+        <v>12000</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9028.799999999999</v>
+        <v>12000</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -930,90 +934,90 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0013</t>
+          <t>СЧ-2026-0012</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="4" t="n">
-        <v>10000</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>9028.799999999999</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>issued</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>credit_note</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>КН-2026-0003</t>
+          <t>СЧ-2026-0013</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="4" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>issued</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>credit_note</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0015</t>
+          <t>КН-2026-0003</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46295</v>
+        <v>46285</v>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="4" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1024,33 +1028,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0029</t>
+          <t>СЧ-2026-0015</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00001</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0030</t>
+          <t>KP-2026-0029</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00106</t>
+          <t>DIM-2026-00001</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>62480</v>
+        <v>9000</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>62480</v>
+        <v>9000</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1170,31 +1170,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0005</t>
+          <t>СЧ-2026-0019</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00040</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="4" t="n">
-        <v>62480</v>
+        <v>12000</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>62480</v>
+        <v>12000</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -1205,33 +1203,29 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0011</t>
+          <t>СЧ-2026-0020</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00044</t>
-        </is>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="4" t="n">
-        <v>62480</v>
+        <v>12000</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>62480</v>
+        <v>12000</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -1247,28 +1241,24 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0006</t>
+          <t>СЧ-2026-0018</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00044</t>
-        </is>
-      </c>
+        <v>46292</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="4" t="n">
-        <v>62480</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>62480</v>
+        <v>1000</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -1279,31 +1269,29 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0006</t>
+          <t>СЧ-2026-0019</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>DIM-2026-00044</t>
-        </is>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="4" t="n">
-        <v>62480</v>
+        <v>1000</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>62480</v>
+        <v>1000</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -1319,14 +1307,14 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0012</t>
+          <t>KP-2026-0031</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1356,28 +1344,28 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0013</t>
+          <t>KP-2026-0032</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00112</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -1388,33 +1376,33 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0014</t>
+          <t>INV-2026-0034</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00112</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -1425,23 +1413,21 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Акт выполненных работ</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0015</t>
+          <t>ACT-2026-0015</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>46291</v>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="D28" s="3" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00057</t>
+          <t>DIM-2026-00112</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
@@ -1863,12 +1849,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>Коммерческое предложение</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0003</t>
+          <t>KP-2026-0021</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -1879,7 +1865,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00024</t>
+          <t>DIM-2026-00077</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
@@ -2009,23 +1995,21 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Акт выполненных работ</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0023</t>
+          <t>ACT-2026-0003</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
         <v>46284</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>46291</v>
-      </c>
+      <c r="D44" s="3" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00085</t>
+          <t>DIM-2026-00024</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
@@ -2739,18 +2723,20 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0003</t>
+          <t>INV-2026-0003</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
         <v>46284</v>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>46291</v>
+      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>DIM-2026-00024</t>
@@ -2779,7 +2765,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0021</t>
+          <t>KP-2026-0006</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -2790,7 +2776,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00077</t>
+          <t>DIM-2026-00027</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
@@ -2811,12 +2797,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Коммерческое предложение</t>
+          <t>Счёт на оплату</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0006</t>
+          <t>INV-2026-0004</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -2848,20 +2834,18 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>Акт выполненных работ</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>INV-2026-0004</t>
+          <t>ACT-2026-0004</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
         <v>46284</v>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>46291</v>
-      </c>
+      <c r="D67" s="3" t="n"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>DIM-2026-00027</t>
@@ -2885,31 +2869,33 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Акт выполненных работ</t>
+          <t>Коммерческое предложение</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ACT-2026-0004</t>
+          <t>KP-2026-0007</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
         <v>46284</v>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>46291</v>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00027</t>
+          <t>DIM-2026-00001</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>62480</v>
+        <v>9000</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>62480</v>
+        <v>9000</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -2925,7 +2911,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0007</t>
+          <t>KP-2026-0008</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -2962,7 +2948,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0008</t>
+          <t>KP-2026-0009</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -2999,7 +2985,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>KP-2026-0009</t>
+          <t>KP-2026-0023</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -3010,17 +2996,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00085</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>9000</v>
+        <v>62480</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -3105,66 +3091,72 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>Акт выполненных работ</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0014</t>
+          <t>ACT-2026-0005</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+        <v>46284</v>
+      </c>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00040</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="n">
-        <v>5000</v>
+        <v>62480</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>5000</v>
+        <v>62480</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>issued</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Счёт на оплату</t>
+          <t>Коммерческое предложение</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0006</t>
+          <t>KP-2026-0011</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>46245</v>
+        <v>46284</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+        <v>46291</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00044</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="n">
-        <v>5000</v>
+        <v>62480</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>5000</v>
+        <v>62480</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>issued</t>
         </is>
       </c>
     </row>
@@ -3176,87 +3168,373 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>СЧ-2026-0010</t>
+          <t>INV-2026-0006</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>46245</v>
+        <v>46284</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+        <v>46291</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00044</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="n">
-        <v>5000</v>
+        <v>62480</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>5000</v>
+        <v>62480</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>issued</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>Акт выполненных работ</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ACT-2026-0006</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00044</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0012</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0013</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0014</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>KP-2026-0015</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00057</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>62480</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
           <t>Счёт на оплату</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0014</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0006</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>СЧ-2026-0010</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Счёт на оплату</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>СЧ-2026-0002</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C85" s="3" t="n">
         <v>46243</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D85" s="3" t="n">
         <v>46231</v>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="4" t="n">
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="4" t="n">
         <v>64800</v>
       </c>
-      <c r="G77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="4" t="n">
+      <c r="G85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="4" t="n">
         <v>64800</v>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>overdue</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="5" t="inlineStr"/>
-      <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
-      <c r="F78" s="5">
-        <f>SUM(F2:F77)</f>
+      <c r="B86" s="5" t="inlineStr"/>
+      <c r="C86" s="5" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="inlineStr"/>
+      <c r="F86" s="5">
+        <f>SUM(F2:F85)</f>
         <v/>
       </c>
-      <c r="G78" s="5">
-        <f>SUM(G2:G77)</f>
+      <c r="G86" s="5">
+        <f>SUM(G2:G85)</f>
         <v/>
       </c>
-      <c r="H78" s="5">
-        <f>SUM(H2:H77)</f>
+      <c r="H86" s="5">
+        <f>SUM(H2:H85)</f>
         <v/>
       </c>
-      <c r="I78" s="5" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
